--- a/futbol_bot/apuestas_soccer.xlsx
+++ b/futbol_bot/apuestas_soccer.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1926,23 +1926,27 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>acertado</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr"/>
+          <t>sin_datos</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2 - 1.</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-06-06T22:21:03.724376</t>
+          <t>2026-06-06T23:02:41.374538</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2110,17 +2114,25 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -2210,17 +2222,25 @@
           <t>Czechia</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -2310,17 +2330,25 @@
           <t>Bosnia-Herzegovina</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2410,17 +2438,25 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2510,17 +2546,25 @@
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2610,17 +2654,25 @@
           <t>Morocco</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2710,17 +2762,25 @@
           <t>Scotland</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2810,17 +2870,25 @@
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2910,17 +2978,25 @@
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -3010,17 +3086,25 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -3110,17 +3194,25 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -3210,17 +3302,25 @@
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -3310,17 +3410,25 @@
           <t>Cape Verde</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -3410,17 +3518,25 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3510,17 +3626,25 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3610,17 +3734,25 @@
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3710,17 +3842,25 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -3810,17 +3950,25 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3910,17 +4058,25 @@
           <t>Algeria</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -4010,17 +4166,25 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -4110,17 +4274,25 @@
           <t>Congo DR</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -4210,17 +4382,25 @@
           <t>Croatia</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -4310,17 +4490,25 @@
           <t>Panama</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -4410,17 +4598,25 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -4510,17 +4706,25 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -4610,17 +4814,25 @@
           <t>Bosnia-Herzegovina</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -4710,17 +4922,25 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -4810,17 +5030,25 @@
           <t>South Korea</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4910,17 +5138,25 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -5010,17 +5246,25 @@
           <t>Morocco</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -5110,17 +5354,25 @@
           <t>Haiti</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -5210,17 +5462,25 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -5310,17 +5570,25 @@
           <t>Sweden</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -5410,17 +5678,25 @@
           <t>Ivory Coast</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -5510,17 +5786,25 @@
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -5584,6 +5868,804 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4159559113272821804</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4068069586459064018</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2606149404735617769</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="P51" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Over 4.5 Corners</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14806177180014657630</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aldosivi</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>AH0 - River Plate</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P52" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Over 4.5 Corners</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10055280371506172102</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sarmiento (Junín)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H53" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="P53" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Over 4.5 Corners</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10229698322051352208</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Godoy Cruz Antonio Tomba</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Mitre (Santiago del Estero)</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1517990362356477695</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AMISTOSOS_INT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>NO_APOSTAR</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—  </t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2026-06-07T06:00:01.466332</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/futbol_bot/apuestas_soccer.xlsx
+++ b/futbol_bot/apuestas_soccer.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,11 +547,66 @@
           <t>hora_partido</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>llm_ah0</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>llm_ou25</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>llm_corners</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>llm_porque</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>llm_favorito</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>llm_ir_favorito</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>llm_goles</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>llm_corners_est</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>llm_tiros_porteria</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>llm_lineas</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>llm_resultado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12476915864228024005</t>
+          <t>17846239333777060613</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -559,39 +614,35 @@
           <t>AMISTOSOS_INT</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>América</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +652,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,32 +662,24 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NO_APOSTAR</t>
+          <t>Over 4.5 Corners</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -660,26 +703,53 @@
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>América tiene un rendimiento inconsistente y Fortaleza juega bien en casa.</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15882949727728216911</t>
+          <t>2778489345574523075</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -687,11 +757,7 @@
           <t>AMISTOSOS_INT</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>New England Revolution</t>
@@ -699,27 +765,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -742,19 +808,11 @@
           <t xml:space="preserve">—  </t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -774,28 +832,28 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4 - 2.</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -803,51 +861,78 @@
           <t>20:00</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Croatia ha mostrado mejor forma en sus últimos partidos.</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5323144714085170816</t>
+          <t>15473778419282972690</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -857,7 +942,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -867,34 +952,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -902,80 +967,111 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1 - 1.</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:00</t>
-        </is>
-      </c>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Czechia tiene mejor ranking y forma reciente.</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Patrik Schick", "equipo": "Czechia", "tiros_estimados": 3}, {"jugador": "Teboho Mokoena", "equipo": "South Africa", "tiros_estimados": 2}, {"jugador": "Vladimír Coufal", "equipo": "Czechia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 60, "over_3.5": 40}, "corners": {"over_8.5": 55, "over_9.5": 45, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2930769702033477213</t>
+          <t>15666946112146566021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimnasia y Esgrima (Jujuy)</t>
+          <t>Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -985,7 +1081,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -995,34 +1091,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1030,80 +1106,111 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4 - 1.</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Switzerland es más fuerte en el ranking y en el juego.</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Xherdan Shaqiri", "equipo": "Switzerland", "tiros_estimados": 4}, {"jugador": "Edin Džeko", "equipo": "Bosnia-Herzegovina", "tiros_estimados": 3}, {"jugador": "Breel Embolo", "equipo": "Switzerland", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 65, "over_3.5": 35}, "corners": {"over_8.5": 50, "over_9.5": 40, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4192390671545971518</t>
+          <t>9960283725073412292</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>San Martín (San Juan)</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1113,7 +1220,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1123,34 +1230,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1158,127 +1245,138 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6 - 0.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Canada tiene mejor ranking y localía.</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Jonathan David", "equipo": "Canada", "tiros_estimados": 3}, {"jugador": "Almoez Ali", "equipo": "Qatar", "tiros_estimados": 2}, {"jugador": "Cyle Larin", "equipo": "Canada", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 65, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 45, "over_9.5": 30, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12399585135176102513</t>
+          <t>12208032235207065497</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AH0 - Arsenal</t>
+          <t>NO_APOSTAR</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Under 2.5</t>
+          <t>NO_APOSTAR</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>4.92</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>9.57</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Over 4.5 Corners</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1286,80 +1384,111 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1 - 0.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Mexico tiene mejor ranking y experiencia en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Hirving Lozano", "equipo": "Mexico", "tiros_estimados": 4}, {"jugador": "Son Heung-min", "equipo": "South Korea", "tiros_estimados": 3}, {"jugador": "Raúl Jiménez", "equipo": "Mexico", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 60, "over_3.5": 35}, "corners": {"over_8.5": 60, "over_9.5": 50, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1743064291890725965</t>
+          <t>11362139699517394478</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fénix</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1369,7 +1498,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1379,34 +1508,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1414,80 +1523,111 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2 - 0.</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>United States es local y tiene mejor ranking.</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Christian Pulisic", "equipo": "United States", "tiros_estimados": 4}, {"jugador": "Mathew Leckie", "equipo": "Australia", "tiros_estimados": 2}, {"jugador": "Gio Reyna", "equipo": "United States", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 75, "over_2.5": 55, "over_3.5": 30}, "corners": {"over_8.5": 50, "over_9.5": 35, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7521404831378766042</t>
+          <t>10772562446516819121</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Leones de Rosario</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1497,7 +1637,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1507,34 +1647,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1542,80 +1662,111 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0 - 1.</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:30</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Racha reciente y calidad de plantilla favorecen a Marruecos.</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Ryan Christie", "equipo": "Scotland", "tiros_estimados": 2}, {"jugador": "Hakim Ziyech", "equipo": "Morocco", "tiros_estimados": 3}, {"jugador": "Youssef En-Nesyri", "equipo": "Morocco", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 70, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 60, "over_9.5": 40, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8387197468704161141</t>
+          <t>3024980047868386797</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yupanqui</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1625,7 +1776,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1635,34 +1786,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1670,28 +1801,24 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>no_apostar</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>no_apostar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3 - 0.</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1699,61 +1826,96 @@
           <t>18:30</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Brasil tiene una plantilla superior y juega en casa.</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Neymar", "equipo": "Brazil", "tiros_estimados": 4}, {"jugador": "Vinícius Júnior", "equipo": "Brazil", "tiros_estimados": 3}, {"jugador": "Richarlison", "equipo": "Brazil", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 85, "over_2.5": 75, "over_3.5": 60}, "corners": {"over_8.5": 70, "over_9.5": 50, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6922854236200119249</t>
+          <t>13731083698475288094</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AH0 - Vitória</t>
+          <t>NO_APOSTAR</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1766,31 +1928,11 @@
           <t>BAJA</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>9.15</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Over 4.5 Corners</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1806,82 +1948,113 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Türkiye juega en casa y tiene mejor racha reciente.</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Cenk Tosun", "equipo": "Türkiye", "tiros_estimados": 3}, {"jugador": "Hakan Çalhanoğlu", "equipo": "Türkiye", "tiros_estimados": 2}, {"jugador": "Miguel Almirón", "equipo": "Paraguay", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 55, "over_3.5": 35}, "corners": {"over_8.5": 55, "over_9.5": 35, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13155048584644479919</t>
+          <t>11217227845594717973</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AH0 - Internacional</t>
+          <t>NO_APOSTAR</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1894,31 +2067,11 @@
           <t>BAJA</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4.51</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>4.64</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>9.15</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Over 4.5 Corners</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -1926,84 +2079,111 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>acertado</t>
+          <t>pendiente</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>no_apostar</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>sin_datos</t>
-        </is>
-      </c>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2 - 1.</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2026-06-06T23:02:41.374538</t>
-        </is>
-      </c>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Holanda tiene ventaja en casa y mejor ranking FIFA.</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Memphis Depay", "equipo": "Netherlands", "tiros_estimados": 3}, {"jugador": "Cody Gakpo", "equipo": "Netherlands", "tiros_estimados": 2}, {"jugador": "Alexander Isak", "equipo": "Sweden", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 70, "over_2.5": 55, "over_3.5": 30}, "corners": {"over_8.5": 50, "over_9.5": 30, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1698146256979582625</t>
+          <t>4387193732010287727</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2013,7 +2193,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2023,34 +2203,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -2066,32 +2226,67 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:03.724376</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Alemania tiene un equipo más fuerte y juega en casa.</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Kai Havertz", "equipo": "Germany", "tiros_estimados": 4}, {"jugador": "Thomas Müller", "equipo": "Germany", "tiros_estimados": 3}, {"jugador": "Wilfried Zaha", "equipo": "Ivory Coast", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 85, "over_2.5": 75, "over_3.5": 55}, "corners": {"over_8.5": 65, "over_9.5": 45, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5140838331256029551</t>
+          <t>18140786275608367363</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2099,39 +2294,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2180,26 +2371,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Ecuador tiene mejor ranking y racha reciente.</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Enner Valencia", "equipo": "Ecuador", "tiros_estimados": 3}, {"jugador": "Michael Estrada", "equipo": "Ecuador", "tiros_estimados": 2}, {"jugador": "Leandro Bacuna", "equipo": "Curaçao", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 60, "over_3.5": 30}, "corners": {"over_8.5": 40, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8918748471286121501</t>
+          <t>16473758932694638852</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2207,39 +2433,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2288,26 +2510,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>02:00</t>
-        </is>
-      </c>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Japan tiene mejor ranking y rendimiento reciente.</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Takumi Minamino", "equipo": "Japan", "tiros_estimados": 3}, {"jugador": "Kaoru Mitoma", "equipo": "Japan", "tiros_estimados": 3}, {"jugador": "Wahbi Khazri", "equipo": "Tunisia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 70, "over_2.5": 55, "over_3.5": 25}, "corners": {"over_8.5": 35, "over_9.5": 25, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18148213342546973659</t>
+          <t>4429990344879757327</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2315,39 +2572,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2396,26 +2649,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Spain es un equipo de élite con gran historial.</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Alvaro Morata", "equipo": "Spain", "tiros_estimados": 4}, {"jugador": "Ferran Torres", "equipo": "Spain", "tiros_estimados": 3}, {"jugador": "Salem Al-Dawsari", "equipo": "Saudi Arabia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 70, "over_3.5": 50}, "corners": {"over_8.5": 50, "over_9.5": 40, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12782195113673287433</t>
+          <t>17560853110533370</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2423,39 +2711,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2504,26 +2788,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Belgium tiene un equipo más fuerte y experiencia.</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Romelu Lukaku", "equipo": "Belgium", "tiros_estimados": 4}, {"jugador": "Kevin De Bruyne", "equipo": "Belgium", "tiros_estimados": 3}, {"jugador": "Sardar Azmoun", "equipo": "Iran", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 65, "over_3.5": 40}, "corners": {"over_8.5": 45, "over_9.5": 35, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6448743273200353908</t>
+          <t>2810772877381770173</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2531,39 +2850,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2612,26 +2927,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Uruguay tiene mejor ranking y experiencia en torneos.</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Luis Suárez", "equipo": "Uruguay", "tiros_estimados": 3}, {"jugador": "Darwin Núñez", "equipo": "Uruguay", "tiros_estimados": 3}, {"jugador": "Ryan Mendes", "equipo": "Cape Verde", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 60, "over_3.5": 30}, "corners": {"over_8.5": 30, "over_9.5": 20, "over_10.5": 10}}</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14900019064495537612</t>
+          <t>13225371111672789552</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2639,39 +2989,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2720,26 +3066,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Egipto tiene mejor ranking y experiencia en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Mohamed Salah", "equipo": "Egypt", "tiros_estimados": 4}, {"jugador": "Omar Marmoush", "equipo": "Egypt", "tiros_estimados": 3}, {"jugador": "Kosta Barbarouses", "equipo": "New Zealand", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 55, "over_3.5": 30}, "corners": {"over_8.5": 40, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8428284172463348947</t>
+          <t>5456405197632123869</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2747,39 +3128,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2828,26 +3205,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Argentina es campeona vigente y tiene un equipo más fuerte.</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Lionel Messi", "equipo": "Argentina", "tiros_estimados": 5}, {"jugador": "Lautaro Martínez", "equipo": "Argentina", "tiros_estimados": 4}, {"jugador": "Marcel Sabitzer", "equipo": "Austria", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 65, "over_3.5": 40}, "corners": {"over_8.5": 50, "over_9.5": 35, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11784227106046974899</t>
+          <t>8048545213706840235</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2855,39 +3267,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2936,26 +3344,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Francia tiene un equipo más talentoso y experiencia mundialista.</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Kylian Mbappé", "equipo": "France", "tiros_estimados": 6}, {"jugador": "Antoine Griezmann", "equipo": "France", "tiros_estimados": 3}, {"jugador": "Mohammed Ali", "equipo": "Iraq", "tiros_estimados": 1}]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 95, "over_1.5": 85, "over_2.5": 75, "over_3.5": 50}, "corners": {"over_8.5": 45, "over_9.5": 30, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13837949563217390153</t>
+          <t>9496900723401038183</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2963,39 +3406,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3044,26 +3483,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Noruega tiene mejor ranking y jugadores destacados.</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Erling Haaland", "equipo": "Norway", "tiros_estimados": 4}, {"jugador": "Alexander Sørloth", "equipo": "Norway", "tiros_estimados": 3}, {"jugador": "Sadio Mané", "equipo": "Senegal", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 65, "over_2.5": 50, "over_3.5": 25}, "corners": {"over_8.5": 35, "over_9.5": 20, "over_10.5": 10}}</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9482498289542478492</t>
+          <t>12541460109236120435</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3071,39 +3545,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3152,26 +3622,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Algeria tiene más experiencia y mejor ranking.</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Youssef Belaili", "equipo": "Algeria", "tiros_estimados": 3}, {"jugador": "Riyad Mahrez", "equipo": "Algeria", "tiros_estimados": 3}, {"jugador": "Baha' Faisal", "equipo": "Jordan", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 75, "over_1.5": 60, "over_2.5": 45, "over_3.5": 20}, "corners": {"over_8.5": 25, "over_9.5": 15, "over_10.5": 5}}</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9334322810156973611</t>
+          <t>11805007377102393285</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3179,39 +3684,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3260,26 +3761,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:00</t>
-        </is>
-      </c>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Portugal tiene un equipo más fuerte y experiencia en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Cristiano Ronaldo", "equipo": "Portugal", "tiros_estimados": 5}, {"jugador": "Bruno Fernandes", "equipo": "Portugal", "tiros_estimados": 3}, {"jugador": "Diogo Jota", "equipo": "Portugal", "tiros_estimados": 4}]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 85, "over_2.5": 75, "over_3.5": 60}, "corners": {"over_8.5": 70, "over_9.5": 60, "over_10.5": 50}}</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8466268238104420849</t>
+          <t>17859521311953187685</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3287,39 +3823,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>England</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3368,26 +3900,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>02:00</t>
-        </is>
-      </c>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Inglaterra tiene un equipo más talentoso y experiencia en torneos internacionales.</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Harry Kane", "equipo": "England", "tiros_estimados": 4}, {"jugador": "Raheem Sterling", "equipo": "England", "tiros_estimados": 3}, {"jugador": "Phil Foden", "equipo": "England", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 80, "over_2.5": 65, "over_3.5": 50}, "corners": {"over_8.5": 65, "over_9.5": 55, "over_10.5": 45}}</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7394512470988345462</t>
+          <t>17110053704824696018</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3395,39 +3962,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3476,26 +4039,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Croacia tiene más experiencia y calidad en el medio campo.</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Luka Modric", "equipo": "Croatia", "tiros_estimados": 3}, {"jugador": "Ivan Perisic", "equipo": "Croatia", "tiros_estimados": 3}, {"jugador": "Andrej Kramaric", "equipo": "Croatia", "tiros_estimados": 4}]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 75, "over_2.5": 55, "over_3.5": 40}, "corners": {"over_8.5": 50, "over_9.5": 40, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>937512089804624175</t>
+          <t>984113063731490342</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3503,39 +4101,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3584,26 +4178,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Colombia tiene un equipo más fuerte y juega en casa.</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Luis Díaz", "equipo": "Colombia", "tiros_estimados": 4}, {"jugador": "Duvan Zapata", "equipo": "Colombia", "tiros_estimados": 3}, {"jugador": "James Rodríguez", "equipo": "Colombia", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 80, "over_2.5": 65, "over_3.5": 50}, "corners": {"over_8.5": 60, "over_9.5": 50, "over_10.5": 40}}</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13494655352058850212</t>
+          <t>1342337427088692320</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3611,39 +4240,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3692,26 +4317,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Bosnia tiene ventaja en calidad y experiencia en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Edin Dzeko", "equipo": "Bosnia-Herzegovina", "tiros_estimados": 4}, {"jugador": "Gojko Cimirot", "equipo": "Bosnia-Herzegovina", "tiros_estimados": 2}, {"jugador": "Rade Krunic", "equipo": "Bosnia-Herzegovina", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 75, "over_2.5": 55, "over_3.5": 40}, "corners": {"over_8.5": 45, "over_9.5": 35, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17516964952615194337</t>
+          <t>12146975419631089187</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3719,39 +4379,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3800,26 +4456,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Su ranking FIFA y racha reciente son superiores.</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Xherdan Shaqiri", "equipo": "Switzerland", "tiros_estimados": 3}, {"jugador": "Breel Embolo", "equipo": "Switzerland", "tiros_estimados": 2}, {"jugador": "Jonathan David", "equipo": "Canada", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 60, "over_3.5": 40}, "corners": {"over_8.5": 45, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3434397816579040720</t>
+          <t>5362542927197070085</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3827,39 +4518,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3908,26 +4595,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Ranking FIFA y rendimiento reciente son favorables.</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Hakim Ziyech", "equipo": "Morocco", "tiros_estimados": 4}, {"jugador": "Youssef En-Nesyri", "equipo": "Morocco", "tiros_estimados": 3}, {"jugador": "Duckens Nazon", "equipo": "Haiti", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 65, "over_3.5": 45}, "corners": {"over_8.5": 40, "over_9.5": 25, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>778294423830816391</t>
+          <t>758677229961365611</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3935,39 +4657,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4016,26 +4734,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Brasil tiene un historial superior y mejor ranking FIFA.</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Neymar", "equipo": "Brazil", "tiros_estimados": 5}, {"jugador": "Richarlison", "equipo": "Brazil", "tiros_estimados": 3}, {"jugador": "Scott McTominay", "equipo": "Scotland", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 70, "over_2.5": 60, "over_3.5": 40}, "corners": {"over_8.5": 35, "over_9.5": 20, "over_10.5": 10}}</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1910700429847776535</t>
+          <t>11509269370541288471</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4043,39 +4796,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4124,26 +4873,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Ranking FIFA y experiencia en mundiales son superiores.</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Raúl Jiménez", "equipo": "Mexico", "tiros_estimados": 3}, {"jugador": "Hirving Lozano", "equipo": "Mexico", "tiros_estimados": 3}, {"jugador": "Patrik Schick", "equipo": "Czechia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 55, "over_3.5": 35}, "corners": {"over_8.5": 50, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>329094686647786936</t>
+          <t>16340357874540499062</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4151,39 +4935,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4232,26 +5012,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Ranking FIFA y racha reciente favorecen a Corea.</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Son Heung-min", "equipo": "South Korea", "tiros_estimados": 4}, {"jugador": "Kwon Chang-hoon", "equipo": "South Korea", "tiros_estimados": 3}, {"jugador": "Percy Tau", "equipo": "South Africa", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 65, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 30, "over_9.5": 15, "over_10.5": 10}}</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>957327462762558492</t>
+          <t>11835620229468527446</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4259,39 +5074,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Congo DR</t>
+          <t>Ivory Coast</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4340,26 +5151,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Mayor ranking FIFA y experiencia en torneos.</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Wilfried Zaha", "equipo": "Ivory Coast", "tiros_estimados": 3}, {"jugador": "Donyell Malen", "equipo": "Ivory Coast", "tiros_estimados": 2}, {"jugador": "Leandro Bacuna", "equipo": "Curaçao", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 40, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10636775725735173790</t>
+          <t>6835389728658256786</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4367,39 +5213,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4448,26 +5290,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Mayor calidad de plantilla y experiencia en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Kai Havertz", "equipo": "Germany", "tiros_estimados": 4}, {"jugador": "Timo Werner", "equipo": "Germany", "tiros_estimados": 3}, {"jugador": "Enner Valencia", "equipo": "Ecuador", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 75, "over_2.5": 55, "over_3.5": 35}, "corners": {"over_8.5": 35, "over_9.5": 25, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>16335546444301717192</t>
+          <t>3652625861961632105</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4475,39 +5352,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4556,26 +5429,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>23:00</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Mayor ranking FIFA y racha reciente positiva.</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Alexander Isak", "equipo": "Sweden", "tiros_estimados": 3}, {"jugador": "Takefusa Kubo", "equipo": "Japan", "tiros_estimados": 2}, {"jugador": "Emil Forsberg", "equipo": "Sweden", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 65, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 45, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16228408283139013422</t>
+          <t>16628360569030648213</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4583,39 +5491,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4664,26 +5568,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>02:00</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Mayor calidad de plantilla y experiencia en torneos.</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Memphis Depay", "equipo": "Netherlands", "tiros_estimados": 4}, {"jugador": "Cody Gakpo", "equipo": "Netherlands", "tiros_estimados": 3}, {"jugador": "Wahbi Khazri", "equipo": "Tunisia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 50, "over_3.5": 25}, "corners": {"over_8.5": 30, "over_9.5": 20, "over_10.5": 10}}</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>225062138541082315</t>
+          <t>8688790061074527198</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4691,39 +5630,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4772,26 +5707,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Racha reciente y ranking FIFA superior.</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Mitchell Duke", "equipo": "Australia", "tiros_estimados": 3}, {"jugador": "Germán Cano", "equipo": "Paraguay", "tiros_estimados": 2}, {"jugador": "Ajdin Hrustic", "equipo": "Australia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 50, "over_3.5": 25}, "corners": {"over_8.5": 40, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1839506352319610449</t>
+          <t>13195940402317546784</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4799,39 +5769,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4880,26 +5846,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Mayor ranking FIFA y mejor racha reciente.</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[{"jugador": "C. Pulisic", "equipo": "United States", "tiros_estimados": 3}, {"jugador": "H. Yilmaz", "equipo": "Türkiye", "tiros_estimados": 2}, {"jugador": "G. Weah", "equipo": "United States", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 55, "over_3.5": 30}, "corners": {"over_8.5": 60, "over_9.5": 40, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11517596368715426364</t>
+          <t>18398064454856537337</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4907,39 +5908,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>France</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4988,26 +5985,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Superioridad en calidad de plantilla y ranking FIFA.</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[{"jugador": "E. Haaland", "equipo": "Norway", "tiros_estimados": 4}, {"jugador": "K. Mbappé", "equipo": "France", "tiros_estimados": 3}, {"jugador": "A. Griezmann", "equipo": "France", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 75, "over_2.5": 60, "over_3.5": 35}, "corners": {"over_8.5": 65, "over_9.5": 45, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8790009415501385448</t>
+          <t>6675765006413583680</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5015,39 +6047,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5096,26 +6124,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Mayor ranking FIFA y ventaja en experiencia.</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[{"jugador": "S. Mané", "equipo": "Senegal", "tiros_estimados": 3}, {"jugador": "K. Diatta", "equipo": "Senegal", "tiros_estimados": 2}, {"jugador": "A. Alaa", "equipo": "Iraq", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 50, "over_3.5": 25}, "corners": {"over_8.5": 55, "over_9.5": 35, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16146807238186448155</t>
+          <t>3326038283785742773</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5123,39 +6186,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5204,26 +6263,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Ambos equipos tienen similitudes, difícil de predecir.</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Cape Verde</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[{"jugador": "D. Gomes", "equipo": "Cape Verde", "tiros_estimados": 2}, {"jugador": "F. Al-Muwallad", "equipo": "Saudi Arabia", "tiros_estimados": 2}, {"jugador": "R. Pereira", "equipo": "Cape Verde", "tiros_estimados": 1}]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 80, "over_1.5": 50, "over_2.5": 30, "over_3.5": 15}, "corners": {"over_8.5": 50, "over_9.5": 30, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3286813840903346286</t>
+          <t>2093904156873605456</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5231,39 +6325,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5312,26 +6402,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>22:00</t>
-        </is>
-      </c>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Mejor ranking FIFA y calidad de plantilla.</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[{"jugador": "L. Suárez", "equipo": "Uruguay", "tiros_estimados": 3}, {"jugador": "F. Torres", "equipo": "Spain", "tiros_estimados": 3}, {"jugador": "D. Olmo", "equipo": "Spain", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 75, "over_2.5": 60, "over_3.5": 30}, "corners": {"over_8.5": 60, "over_9.5": 40, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14338328398336320549</t>
+          <t>2887539908949937079</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5339,39 +6464,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5420,26 +6541,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>00:30</t>
-        </is>
-      </c>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Egipto tiene mejor ranking FIFA y racha reciente.</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Mohamed Salah", "equipo": "Egypt", "tiros_estimados": 4}, {"jugador": "Tamer Hossam", "equipo": "Egypt", "tiros_estimados": 2}, {"jugador": "Sardar Azmoun", "equipo": "Iran", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 40, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1733224280357127435</t>
+          <t>17723213279760554811</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5447,39 +6603,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5528,26 +6680,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>03:00</t>
-        </is>
-      </c>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Bélgica es un equipo de élite con mejor ranking y experiencia.</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Romelu Lukaku", "equipo": "Belgium", "tiros_estimados": 5}, {"jugador": "Kevin De Bruyne", "equipo": "Belgium", "tiros_estimados": 3}, {"jugador": "Chris Wood", "equipo": "New Zealand", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 65, "over_3.5": 45}, "corners": {"over_8.5": 55, "over_9.5": 40, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14912475289314398492</t>
+          <t>6392033486487619641</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5555,39 +6742,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5636,26 +6819,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Croacia tiene mejor ranking y experiencia en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Luka Modric", "equipo": "Croatia", "tiros_estimados": 3}, {"jugador": "Andrej Kramaric", "equipo": "Croatia", "tiros_estimados": 4}, {"jugador": "Jordan Ayew", "equipo": "Ghana", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 55, "over_3.5": 30}, "corners": {"over_8.5": 35, "over_9.5": 25, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>11426648169589114741</t>
+          <t>7871628305316138959</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5663,39 +6881,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ivory Coast</t>
+          <t>England</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5744,26 +6958,61 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>20:00</t>
-        </is>
-      </c>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Inglaterra es un equipo fuerte con gran ranking y calidad.</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Harry Kane", "equipo": "England", "tiros_estimados": 5}, {"jugador": "Raheem Sterling", "equipo": "England", "tiros_estimados": 3}, {"jugador": "Gabriel Torres", "equipo": "Panama", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 70, "over_3.5": 50}, "corners": {"over_8.5": 60, "over_9.5": 45, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6698153050980846156</t>
+          <t>7325014163923207632</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5771,39 +7020,35 @@
           <t>MUNDIAL</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5852,59 +7097,98 @@
           <t>0-0</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>2026-06-06T22:21:19.199321</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Portugal tiene mejor ranking y racha reciente.</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Luis Díaz", "equipo": "Colombia", "tiros_estimados": 3}, {"jugador": "Cristiano Ronaldo", "equipo": "Portugal", "tiros_estimados": 4}, {"jugador": "Duván Zapata", "equipo": "Colombia", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 55, "over_3.5": 35}, "corners": {"over_8.5": 50, "over_9.5": 35, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4159559113272821804</t>
+          <t>9070793410968111948</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -5913,7 +7197,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5923,28 +7207,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -5960,65 +7230,104 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Uzbekistan tiene mejor ranking y forma reciente.</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Dieumerci Mbokani", "equipo": "Congo DR", "tiros_estimados": 3}, {"jugador": "Eldor Shomurodov", "equipo": "Uzbekistan", "tiros_estimados": 4}, {"jugador": "Oston Urunov", "equipo": "Uzbekistan", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 70, "over_2.5": 50, "over_3.5": 30}, "corners": {"over_8.5": 40, "over_9.5": 30, "over_10.5": 20}}</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4068069586459064018</t>
+          <t>2524670912555559584</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Málaga</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -6027,7 +7336,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -6037,28 +7346,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -6074,65 +7369,104 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Algeria tiene un mejor rendimiento en el torneo y localía.</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Riyad Mahrez", "equipo": "Algeria", "tiros_estimados": 4}, {"jugador": "Youssef Atal", "equipo": "Algeria", "tiros_estimados": 3}, {"jugador": "Marko Arnautovic", "equipo": "Austria", "tiros_estimados": 3}]</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 75, "over_2.5": 55, "over_3.5": 35}, "corners": {"over_8.5": 35, "over_9.5": 25, "over_10.5": 15}}</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2606149404735617769</t>
+          <t>6530897504493972133</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tigres UANL</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.34</v>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -6154,25 +7488,11 @@
           <t>BAJA</t>
         </is>
       </c>
-      <c r="N51" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="O51" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="P51" t="n">
-        <v>8.84</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Over 4.5 Corners</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -6188,74 +7508,113 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Argentina es claramente superior en calidad y experiencia.</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Lionel Messi", "equipo": "Argentina", "tiros_estimados": 5}, {"jugador": "Julian Alvarez", "equipo": "Argentina", "tiros_estimados": 4}, {"jugador": "Mohammad Abu Zreiq", "equipo": "Jordan", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 95, "over_1.5": 85, "over_2.5": 70, "over_3.5": 50}, "corners": {"over_8.5": 20, "over_9.5": 15, "over_10.5": 10}}</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>14806177180014657630</t>
+          <t>12812922739934051490</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+          <t>MUNDIAL</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>Group A 2nd Place</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.42</v>
+          <t>Group B 2nd Place</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>AH0 - River Plate</t>
+          <t>NO_APOSTAR</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6268,25 +7627,11 @@
           <t>BAJA</t>
         </is>
       </c>
-      <c r="N52" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="O52" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="P52" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Over 4.5 Corners</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -6302,65 +7647,100 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>2026-06-07T06:00:01.466332</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Falta información específica sobre equipos y contexto.</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10055280371506172102</t>
+          <t>16599065049895485617</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
+          <t>MUNDIAL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-06-07T06:00:01.466332</t>
+          <t>2026-06-20T22:59:59.607438</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sarmiento (Junín)</t>
+          <t>Group C Winner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.23</v>
+          <t>Group F 2nd Place</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -6382,25 +7762,11 @@
           <t>BAJA</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="P53" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Over 4.5 Corners</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -6416,65 +7782,116 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-06-07T06:00:01.466332</t>
+          <t>2026-06-20T23:13:39.049501</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>04:00</t>
-        </is>
-      </c>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>["Grupo C puede incluir a un favorito fuerte", "Grupo F 2nd Place puede ser débil", "Presión de avanzar en el torneo"]</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Grupo C probablemente tiene un equipo fuerte.</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Group C Winner</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Jugador A", "equipo": "Group C Winner", "tiros_estimados": 3}, {"jugador": "Jugador B", "equipo": "Group F 2nd Place", "tiros_estimados": 2}, {"jugador": "Jugador C", "equipo": "Group C Winner", "tiros_estimados": 4}]</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 65, "over_3.5": 40}, "corners": {"over_8.5": 60, "over_9.5": 50, "over_10.5": 30}}</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10229698322051352208</t>
+          <t>6990928606843208652</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
+          <t>MUNDIAL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-06-07T06:00:01.466332</t>
+          <t>2026-06-20T22:59:59.607438</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Godoy Cruz Antonio Tomba</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mitre (Santiago del Estero)</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
+          <t>Third Place Group A/B/C/D/F</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -6483,7 +7900,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6493,28 +7910,14 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -6530,65 +7933,116 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-06-07T06:00:01.466332</t>
+          <t>2026-06-20T23:13:39.816502</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>["Alemania tiene un historial sólido en mundiales", "Tercero de grupo puede ser débil", "Presión de ganar para avanzar"]</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Alemania históricamente fuerte en mundiales.</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Jugador D", "equipo": "Alemania", "tiros_estimados": 5}, {"jugador": "Jugador E", "equipo": "Alemania", "tiros_estimados": 4}, {"jugador": "Jugador F", "equipo": "Third Place Group A/B/C/D/F", "tiros_estimados": 2}]</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 90, "over_1.5": 80, "over_2.5": 70, "over_3.5": 50}, "corners": {"over_8.5": 70, "over_9.5": 60, "over_10.5": 40}}</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1517990362356477695</t>
+          <t>12824075930464103939</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMISTOSOS_INT</t>
+          <t>MUNDIAL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-06-07T06:00:01.466332</t>
+          <t>2026-06-20T22:59:59.607438</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Group F Winner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Boston River</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
+          <t>Group C 2nd Place</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -6597,7 +8051,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
+          <t>BAJA</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6607,28 +8061,14 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>NO_APOSTAR</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—  </t>
-        </is>
-      </c>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>pendiente</t>
@@ -6644,27 +8084,70 @@
           <t>pendiente</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-06-07T06:00:01.466332</t>
+          <t>2026-06-20T23:13:41.010506</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:30</t>
-        </is>
-      </c>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>["Grupo F Winner probablemente tiene un equipo fuerte", "Grupo C 2nd Place puede ser más débil", "Importancia del partido para avanzar"]</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Grupo F Winner puede ser un equipo fuerte.</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Group F Winner</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[{"jugador": "Jugador G", "equipo": "Group F Winner", "tiros_estimados": 4}, {"jugador": "Jugador H", "equipo": "Group C 2nd Place", "tiros_estimados": 3}, {"jugador": "Jugador I", "equipo": "Group F Winner", "tiros_estimados": 5}]</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>{"goles": {"over_0.5": 85, "over_1.5": 75, "over_2.5": 65, "over_3.5": 35}, "corners": {"over_8.5": 55, "over_9.5": 45, "over_10.5": 25}}</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
